--- a/UHI_Systematic_Review_Database.xlsx
+++ b/UHI_Systematic_Review_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\UHI-Study-in-Savar-Bangladesh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ibrahimkhalil/WorkSpace/Projects &amp; Work/UHI-Study-Savar-Bangladesh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED9B9DC-9B5D-4572-8B5B-B8DA0F80D636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017D271D-0EF6-8A42-A50F-11300D213840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="20740" windowHeight="11320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Literature Review" sheetId="1" r:id="rId1"/>
@@ -63,6 +63,7 @@
         <sz val="11"/>
         <color rgb="FF0000FF"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>https://agupubs.onlinelibrary.wiley.com/doi/epdf/10.1029/GL017i013p02377?saml_referrer</t>
     </r>
@@ -72,6 +73,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> AGU</t>
     </r>
@@ -187,6 +189,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 ◼ Objectives:
@@ -223,11 +226,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -235,6 +240,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -246,12 +252,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -572,18 +580,18 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:G1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="26.85546875" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
-    <col min="6" max="6" width="30.5703125" customWidth="1"/>
-    <col min="7" max="7" width="34.140625" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" customWidth="1"/>
+    <col min="6" max="6" width="30.5" customWidth="1"/>
+    <col min="7" max="7" width="34.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30">
+    <row r="1" spans="1:7" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +614,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="409.5">
+    <row r="2" spans="1:7" ht="380">
       <c r="A2" s="11" t="s">
         <v>19</v>
       </c>
@@ -9624,13 +9632,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="42.85546875" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="42.83203125" customWidth="1"/>
+    <col min="2" max="2" width="34.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" customWidth="1"/>
     <col min="4" max="4" width="68" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="5" max="5" width="34.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -13060,9 +13068,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:A1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="79.5703125" customWidth="1"/>
+    <col min="1" max="1" width="79.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="30.75" customHeight="1">
